--- a/CarMix_2007_2024_DST_BIL10.xlsx
+++ b/CarMix_2007_2024_DST_BIL10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/s224028_dtu_dk/Documents/Elektrotekniologi - Master/2. semester/12100 Quantitative methods to assess sustainability/12100-Quantitative-Group-9/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7610CE85-B6AB-4459-9CCE-2A61159345C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{7610CE85-B6AB-4459-9CCE-2A61159345C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A2398DE-0FB2-4617-B936-6FD1E8B7F216}"/>
   <bookViews>
-    <workbookView xWindow="1150" yWindow="0" windowWidth="14400" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21855" yWindow="1560" windowWidth="18405" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BIL10" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="37">
   <si>
     <t>Bestanden af personbiler pr. 1. januar efter egenvægt, drivmiddel og tid</t>
   </si>
@@ -141,13 +141,20 @@
   </si>
   <si>
     <t>% El-bil fra i alt</t>
+  </si>
+  <si>
+    <t>% El-bil ift. Benzin og Diesel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="167" formatCode="0.000000"/>
+    <numFmt numFmtId="168" formatCode="0.0000000"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -171,6 +178,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -202,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -215,10 +229,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -521,26 +538,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:T24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.7265625" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" customWidth="1"/>
-    <col min="3" max="3" width="17.90625" customWidth="1"/>
-    <col min="4" max="20" width="10" customWidth="1"/>
+    <col min="1" max="1" width="76.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
@@ -596,7 +613,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
@@ -658,7 +675,7 @@
         <v>1796437</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
@@ -717,7 +734,7 @@
         <v>708176</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>23</v>
       </c>
@@ -776,7 +793,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
@@ -835,7 +852,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>26</v>
       </c>
@@ -894,7 +911,7 @@
         <v>200108</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>27</v>
       </c>
@@ -953,7 +970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>28</v>
       </c>
@@ -1012,7 +1029,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
@@ -1071,7 +1088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
@@ -1130,7 +1147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
@@ -1189,7 +1206,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>32</v>
       </c>
@@ -1248,8 +1265,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="B15" s="7" t="s">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C15">
@@ -1325,7 +1342,7 @@
         <v>2827864</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>35</v>
       </c>
@@ -1402,9 +1419,373 @@
         <v>7.0762950410627953E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="145" x14ac:dyDescent="0.35">
-      <c r="A18" s="6" t="s">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17">
+        <f>C8/(C4+C5)</f>
+        <v>7.4263124150615519E-5</v>
+      </c>
+      <c r="D17">
+        <f t="shared" ref="D17:T17" si="2">D8/(D4+D5)</f>
+        <v>6.8654255717763327E-5</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="2"/>
+        <v>6.6700747572450119E-5</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="2"/>
+        <v>1.032983298216618E-4</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="2"/>
+        <v>1.3682451562503612E-4</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="2"/>
+        <v>3.409107460164875E-4</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="2"/>
+        <v>5.568150715460331E-4</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="2"/>
+        <v>6.7471166618640317E-4</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="2"/>
+        <v>1.2546398895538658E-3</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="2"/>
+        <v>3.3111568102242883E-3</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="2"/>
+        <v>3.5274417210592588E-3</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="2"/>
+        <v>3.4791603652780988E-3</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="2"/>
+        <v>3.8917506286241612E-3</v>
+      </c>
+      <c r="P17">
+        <f t="shared" si="2"/>
+        <v>5.9048259490959605E-3</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="2"/>
+        <v>1.1978976869296687E-2</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="2"/>
+        <v>2.5204624392067561E-2</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="2"/>
+        <v>4.3618364665539887E-2</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="2"/>
+        <v>7.9895776313546246E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="168" x14ac:dyDescent="0.35">
+      <c r="A19" s="7" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="8">
+        <f>SUM(C11:C21)</f>
+        <v>2020013.0001485201</v>
+      </c>
+      <c r="D22" s="8">
+        <f t="shared" ref="D22:T22" si="3">SUM(D11:D21)</f>
+        <v>2068493.0001373033</v>
+      </c>
+      <c r="E22" s="8">
+        <f t="shared" si="3"/>
+        <v>2099090.0001333966</v>
+      </c>
+      <c r="F22" s="8">
+        <f t="shared" si="3"/>
+        <v>2120322.0002065841</v>
+      </c>
+      <c r="G22" s="8">
+        <f t="shared" si="3"/>
+        <v>2163676.0002736286</v>
+      </c>
+      <c r="H22" s="8">
+        <f t="shared" si="3"/>
+        <v>2197831.0006817011</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="3"/>
+        <v>2233611.0011133133</v>
+      </c>
+      <c r="J22" s="8">
+        <f t="shared" si="3"/>
+        <v>2278140.0013489514</v>
+      </c>
+      <c r="K22" s="8">
+        <f t="shared" si="3"/>
+        <v>2329597.0025076568</v>
+      </c>
+      <c r="L22" s="8">
+        <f t="shared" si="3"/>
+        <v>2391379.0066104392</v>
+      </c>
+      <c r="M22" s="8">
+        <f t="shared" si="3"/>
+        <v>2466639.0070406706</v>
+      </c>
+      <c r="N22" s="8">
+        <f t="shared" si="3"/>
+        <v>2531824.006943523</v>
+      </c>
+      <c r="O22" s="8">
+        <f t="shared" si="3"/>
+        <v>2599637.007760365</v>
+      </c>
+      <c r="P22" s="8">
+        <f t="shared" si="3"/>
+        <v>2661565.0117527153</v>
+      </c>
+      <c r="Q22" s="8">
+        <f t="shared" si="3"/>
+        <v>2753363.023685988</v>
+      </c>
+      <c r="R22" s="8">
+        <f t="shared" si="3"/>
+        <v>2865411.0491001345</v>
+      </c>
+      <c r="S22" s="8">
+        <f t="shared" si="3"/>
+        <v>2906022.083843621</v>
+      </c>
+      <c r="T22" s="8">
+        <f t="shared" si="3"/>
+        <v>2950864.1506587267</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="9">
+        <f>C8/C22</f>
+        <v>7.4256947845866019E-5</v>
+      </c>
+      <c r="D23" s="10">
+        <f>D8/D22</f>
+        <v>6.8649011618881123E-5</v>
+      </c>
+      <c r="E23" s="9">
+        <f t="shared" ref="E23:T23" si="4">E8/E22</f>
+        <v>6.6695568075262636E-5</v>
+      </c>
+      <c r="F23" s="10">
+        <f t="shared" si="4"/>
+        <v>1.0328619897292143E-4</v>
+      </c>
+      <c r="G23" s="9">
+        <f t="shared" si="4"/>
+        <v>1.3680421651049717E-4</v>
+      </c>
+      <c r="H23" s="10">
+        <f t="shared" si="4"/>
+        <v>3.4079053383434971E-4</v>
+      </c>
+      <c r="I23" s="9">
+        <f t="shared" si="4"/>
+        <v>5.5649797542206027E-4</v>
+      </c>
+      <c r="J23" s="10">
+        <f t="shared" si="4"/>
+        <v>6.7423424332591097E-4</v>
+      </c>
+      <c r="K23" s="9">
+        <f t="shared" si="4"/>
+        <v>1.2530064199335292E-3</v>
+      </c>
+      <c r="L23" s="10">
+        <f t="shared" si="4"/>
+        <v>3.2985151990526664E-3</v>
+      </c>
+      <c r="M23" s="9">
+        <f t="shared" si="4"/>
+        <v>3.5116609991472413E-3</v>
+      </c>
+      <c r="N23" s="10">
+        <f t="shared" si="4"/>
+        <v>3.4619309936085615E-3</v>
+      </c>
+      <c r="O23" s="9">
+        <f t="shared" si="4"/>
+        <v>3.8609236482008156E-3</v>
+      </c>
+      <c r="P23" s="10">
+        <f t="shared" si="4"/>
+        <v>5.8262713597171181E-3</v>
+      </c>
+      <c r="Q23" s="9">
+        <f t="shared" si="4"/>
+        <v>1.1580746790633334E-2</v>
+      </c>
+      <c r="R23" s="10">
+        <f t="shared" si="4"/>
+        <v>2.324622850216149E-2</v>
+      </c>
+      <c r="S23" s="9">
+        <f t="shared" si="4"/>
+        <v>3.8772589040676819E-2</v>
+      </c>
+      <c r="T23" s="10">
+        <f t="shared" si="4"/>
+        <v>6.7813355608162956E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="9">
+        <f>C8/(C4+C5)</f>
+        <v>7.4263124150615519E-5</v>
+      </c>
+      <c r="D24" s="9">
+        <f t="shared" ref="D24:T24" si="5">D8/(D4+D5)</f>
+        <v>6.8654255717763327E-5</v>
+      </c>
+      <c r="E24" s="9">
+        <f t="shared" si="5"/>
+        <v>6.6700747572450119E-5</v>
+      </c>
+      <c r="F24" s="9">
+        <f t="shared" si="5"/>
+        <v>1.032983298216618E-4</v>
+      </c>
+      <c r="G24" s="9">
+        <f t="shared" si="5"/>
+        <v>1.3682451562503612E-4</v>
+      </c>
+      <c r="H24" s="9">
+        <f t="shared" si="5"/>
+        <v>3.409107460164875E-4</v>
+      </c>
+      <c r="I24" s="9">
+        <f t="shared" si="5"/>
+        <v>5.568150715460331E-4</v>
+      </c>
+      <c r="J24" s="9">
+        <f t="shared" si="5"/>
+        <v>6.7471166618640317E-4</v>
+      </c>
+      <c r="K24" s="9">
+        <f t="shared" si="5"/>
+        <v>1.2546398895538658E-3</v>
+      </c>
+      <c r="L24" s="9">
+        <f t="shared" si="5"/>
+        <v>3.3111568102242883E-3</v>
+      </c>
+      <c r="M24" s="9">
+        <f t="shared" si="5"/>
+        <v>3.5274417210592588E-3</v>
+      </c>
+      <c r="N24" s="9">
+        <f t="shared" si="5"/>
+        <v>3.4791603652780988E-3</v>
+      </c>
+      <c r="O24" s="9">
+        <f t="shared" si="5"/>
+        <v>3.8917506286241612E-3</v>
+      </c>
+      <c r="P24" s="9">
+        <f t="shared" si="5"/>
+        <v>5.9048259490959605E-3</v>
+      </c>
+      <c r="Q24" s="9">
+        <f t="shared" si="5"/>
+        <v>1.1978976869296687E-2</v>
+      </c>
+      <c r="R24" s="9">
+        <f t="shared" si="5"/>
+        <v>2.5204624392067561E-2</v>
+      </c>
+      <c r="S24" s="9">
+        <f t="shared" si="5"/>
+        <v>4.3618364665539887E-2</v>
+      </c>
+      <c r="T24" s="9">
+        <f t="shared" si="5"/>
+        <v>7.9895776313546246E-2</v>
       </c>
     </row>
   </sheetData>
